--- a/output/北塩原村_財源構成案.xlsx
+++ b/output/北塩原村_財源構成案.xlsx
@@ -25,9 +25,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -70,7 +71,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -127,6 +128,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3F3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -154,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -240,13 +246,31 @@
     <xf numFmtId="3" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -614,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -850,11 +874,11 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>令和11年度 給付費推計</t>
+          <t>令和11年度 給付費推計（低位）</t>
         </is>
       </c>
       <c r="B12" s="9">
-        <f>'08_R9R11推計'!B11</f>
+        <f>'08_R9R11推計'!E16</f>
         <v/>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -869,60 +893,86 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>伸び率を入力欄で調整する試算。見込量確定後に置き換える</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+          <t>介護給付費 年+2.2%（直近1年）シナリオ。見込量確定後に積上げへ置き換える</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度 給付費推計（中位）</t>
+        </is>
+      </c>
+      <c r="B13" s="5">
+        <f>'08_R9R11推計'!F16</f>
+        <v/>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>08_R9R11推計</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>暫定</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>介護給付費 年+8.4%（令和2〜7年度CAGR）シナリオ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>本ブックの使い方と留意点</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>1. 02・03シートの給付実績は受領データ（令和2〜7年度）の確定値です。原則として変更しません。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2. 財源構成（04・05）は、01_負担区分マスタの負担割合を掛けた法定ベースの試算です。国庫負担基準額を超えた分は村負担となるため、実際の決算額とは一致しません。</t>
+          <t>1. 02・03シートの給付実績は受領データ（令和2〜7年度）の確定値です。原則として変更しません。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>3. 村の歳入歳出決算（障害者自立支援給付費負担金・障害児施設給付費負担金等）を受領したら、09_村確認事項の該当行を更新し、試算値と決算額の差を確認してください。</t>
+          <t>2. 財源構成（04・05）は、01_負担区分マスタの負担割合を掛けた法定ベースの試算です。国庫負担基準額を超えた分は村負担となるため、実際の決算額とは一致しません。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>4. 地域生活支援事業（06）は国1/2以内・県1/4以内の統合補助金です。補助基準額を超える部分は全額村負担となるため、事業費・交付額・村負担を分けて把握する必要があります。</t>
+          <t>3. 村の歳入歳出決算（障害者自立支援給付費負担金・障害児施設給付費負担金等）を受領したら、09_村確認事項の該当行を更新し、試算値と決算額の差を確認してください。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>4. 地域生活支援事業（06）は国1/2以内・県1/4以内の統合補助金です。補助基準額を超える部分は全額村負担となるため、事業費・交付額・村負担を分けて把握する必要があります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>5. 計画書への掲載は、金額の羅列ではなく「総額の推移」「財源別構成比の推移」「サービス別の構成」の3点に絞ると読みやすくなります。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
   </mergeCells>
@@ -4973,17 +5023,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4996,583 +5047,956 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>令和8年度見込を起点に、年伸び率を掛けた試算です。伸び率は黄色セルで調整できます。サービス見込量が確定したら、見込量×単価による積上げに置き換えてください。単位：円。</t>
+          <t>給付費の年次変動が大きく、単一の伸び率では幅を表現できないため、低位・中位の2シナリオで示します。障害児給付費は対象児童の卒業・転入により大きく動くため、伸び率法を用いず令和7年度実績を横置きし、個別ケースによる増減を加算欄で調整します。サービス見込量が確定したら積上げに置き換えてください。単位：円。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>年伸び率（自立支援給付）</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>初期値2.0％は令和6→令和7年度の介護給付費の伸び（＋2.2％）を踏まえた仮置きです。利用者の増減・報酬改定・重度化の見通しを踏まえて村と協議のうえ確定してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>シナリオ設定（黄色セルが入力欄）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>低位シナリオ</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>中位シナリオ</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>根拠・考え方</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>介護給付費 年伸び率</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="C6" s="29" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>低位＝令和6→7年度の実績伸び率（＋2.2％）／中位＝令和2→7年度のCAGR（＋8.4％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>障害児給付費</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>令和7年度実績を横置き</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>同左</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr"/>
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr"/>
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>令和4年度4,030千円→令和7年度1,636千円と3年で約6割減。対象児童の個別事情で動くため伸び率法は用いない</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>障害児給付費 個別加算（年額）</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>←低位・中位で共通</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>新規利用・卒業・転出入の見込みを金額で入力する（減額はマイナスで入力）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>給付費・財源構成の推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>年度</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>自立支援給付計</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>国庫負担</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>県負担</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>村負担</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>対令和7年度</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>介護給付費
+低位</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>介護給付費
+中位</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>障害児
+給付費</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>計
+低位</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>計
+中位</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>村負担
+低位</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>村負担
+中位</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>区分・備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="B12" s="27">
+        <f>'02_給付実績_介護給付費'!H20</f>
+        <v/>
+      </c>
+      <c r="C12" s="27">
+        <f>B12</f>
+        <v/>
+      </c>
+      <c r="D12" s="27">
+        <f>'03_給付実績_障害児給付費'!H10</f>
+        <v/>
+      </c>
+      <c r="E12" s="27">
+        <f>B12+D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="27">
+        <f>C12+D12</f>
+        <v/>
+      </c>
+      <c r="G12" s="27">
+        <f>ROUND(E12*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="27">
+        <f>ROUND(F12*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
+        <v/>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>実績／受領データによる確定値</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="B13" s="27">
+        <f>ROUND(B12*(1+$B$6),0)</f>
+        <v/>
+      </c>
+      <c r="C13" s="27">
+        <f>ROUND(C12*(1+$C$6),0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="27">
+        <f>D12+N($B$8)</f>
+        <v/>
+      </c>
+      <c r="E13" s="27">
+        <f>B13+D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="27">
+        <f>C13+D13</f>
+        <v/>
+      </c>
+      <c r="G13" s="27">
+        <f>ROUND(E13*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="27">
+        <f>ROUND(F13*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
+        <v/>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>見込／現行計画最終年度。村の最新見込を受領したら実額に差し替える</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="B14" s="27">
+        <f>ROUND(B13*(1+$B$6),0)</f>
+        <v/>
+      </c>
+      <c r="C14" s="27">
+        <f>ROUND(C13*(1+$C$6),0)</f>
+        <v/>
+      </c>
+      <c r="D14" s="27">
+        <f>D12+N($B$8)</f>
+        <v/>
+      </c>
+      <c r="E14" s="27">
+        <f>B14+D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="27">
+        <f>C14+D14</f>
+        <v/>
+      </c>
+      <c r="G14" s="27">
+        <f>ROUND(E14*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="27">
+        <f>ROUND(F14*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
+        <v/>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>推計／次期計画1年目</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="B15" s="27">
+        <f>ROUND(B14*(1+$B$6),0)</f>
+        <v/>
+      </c>
+      <c r="C15" s="27">
+        <f>ROUND(C14*(1+$C$6),0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="27">
+        <f>D12+N($B$8)</f>
+        <v/>
+      </c>
+      <c r="E15" s="27">
+        <f>B15+D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="27">
+        <f>C15+D15</f>
+        <v/>
+      </c>
+      <c r="G15" s="27">
+        <f>ROUND(E15*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="27">
+        <f>ROUND(F15*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
+        <v/>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>推計／次期計画2年目</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="B16" s="27">
+        <f>ROUND(B15*(1+$B$6),0)</f>
+        <v/>
+      </c>
+      <c r="C16" s="27">
+        <f>ROUND(C15*(1+$C$6),0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="27">
+        <f>D12+N($B$8)</f>
+        <v/>
+      </c>
+      <c r="E16" s="27">
+        <f>B16+D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="27">
+        <f>C16+D16</f>
+        <v/>
+      </c>
+      <c r="G16" s="27">
+        <f>ROUND(E16*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="27">
+        <f>ROUND(F16*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
+        <v/>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>推計／次期計画目標年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>低位と中位の差</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="inlineStr"/>
+      <c r="C17" s="31" t="inlineStr"/>
+      <c r="D17" s="31" t="inlineStr"/>
+      <c r="E17" s="31">
+        <f>F16-E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="31" t="inlineStr"/>
+      <c r="G17" s="31">
+        <f>H16-G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="31" t="inlineStr"/>
+      <c r="I17" s="32" t="inlineStr">
+        <is>
+          <t>令和11年度における両シナリオの差（左：給付費／右：村負担）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>伸び率を単一値で置けない理由（実績の年次変動）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>介護給付費</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>前年度比</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>障害児給付費</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>前年度比</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>令和2年度</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>36002274</v>
+      </c>
+      <c r="C21" s="33" t="n"/>
+      <c r="D21" s="5" t="n">
+        <v>746064</v>
+      </c>
+      <c r="E21" s="33" t="n"/>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>基準年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>令和3年度</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>45991635</v>
+      </c>
+      <c r="C22" s="34" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>3254621</v>
+      </c>
+      <c r="E22" s="34" t="n">
+        <v>3.362</v>
+      </c>
+      <c r="F22" s="8" t="inlineStr"/>
+      <c r="G22" s="8" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr"/>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>共同生活援助・就労継続支援B型の増</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>令和4年度</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>44234021</v>
+      </c>
+      <c r="C23" s="33" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>4030423</v>
+      </c>
+      <c r="E23" s="33" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>障害児給付費のピーク</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>令和5年度</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>44419974</v>
+      </c>
+      <c r="C24" s="34" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>3577832</v>
+      </c>
+      <c r="E24" s="34" t="n">
+        <v>-0.112</v>
+      </c>
+      <c r="F24" s="8" t="inlineStr"/>
+      <c r="G24" s="8" t="inlineStr"/>
+      <c r="H24" s="8" t="inlineStr"/>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>ほぼ横ばい</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>52698808</v>
+      </c>
+      <c r="C25" s="33" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1641275</v>
+      </c>
+      <c r="E25" s="33" t="n">
+        <v>-0.541</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>介護は大幅増、障害児は大幅減</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>令和7年度</t>
         </is>
       </c>
-      <c r="B7" s="27">
-        <f>'04_財源構成試算'!D11</f>
-        <v/>
-      </c>
-      <c r="C7" s="27">
-        <f>ROUND(B7*'01_負担区分マスタ'!$C$6,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="27">
-        <f>ROUND(B7*'01_負担区分マスタ'!$D$6,0)</f>
-        <v/>
-      </c>
-      <c r="E7" s="27">
-        <f>B7-C7-D7</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
-        <f>B7/B$7-1</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>実績</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>受領データによる確定値</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>令和8年度</t>
-        </is>
-      </c>
-      <c r="B8" s="27">
-        <f>ROUND(B7*(1+$B$4),0)</f>
-        <v/>
-      </c>
-      <c r="C8" s="27">
-        <f>ROUND(B8*'01_負担区分マスタ'!$C$6,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="27">
-        <f>ROUND(B8*'01_負担区分マスタ'!$D$6,0)</f>
-        <v/>
-      </c>
-      <c r="E8" s="27">
-        <f>B8-C8-D8</f>
-        <v/>
-      </c>
-      <c r="F8" s="19">
-        <f>B8/B$7-1</f>
-        <v/>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>見込</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>現行計画最終年度。村の最新見込に差し替える</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="B9" s="27">
-        <f>ROUND(B8*(1+$B$4),0)</f>
-        <v/>
-      </c>
-      <c r="C9" s="27">
-        <f>ROUND(B9*'01_負担区分マスタ'!$C$6,0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="27">
-        <f>ROUND(B9*'01_負担区分マスタ'!$D$6,0)</f>
-        <v/>
-      </c>
-      <c r="E9" s="27">
-        <f>B9-C9-D9</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
-        <f>B9/B$7-1</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>推計</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>次期計画1年目</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
-        </is>
-      </c>
-      <c r="B10" s="27">
-        <f>ROUND(B9*(1+$B$4),0)</f>
-        <v/>
-      </c>
-      <c r="C10" s="27">
-        <f>ROUND(B10*'01_負担区分マスタ'!$C$6,0)</f>
-        <v/>
-      </c>
-      <c r="D10" s="27">
-        <f>ROUND(B10*'01_負担区分マスタ'!$D$6,0)</f>
-        <v/>
-      </c>
-      <c r="E10" s="27">
-        <f>B10-C10-D10</f>
-        <v/>
-      </c>
-      <c r="F10" s="19">
-        <f>B10/B$7-1</f>
-        <v/>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>推計</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>次期計画2年目</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="B11" s="27">
-        <f>ROUND(B10*(1+$B$4),0)</f>
-        <v/>
-      </c>
-      <c r="C11" s="27">
-        <f>ROUND(B11*'01_負担区分マスタ'!$C$6,0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="27">
-        <f>ROUND(B11*'01_負担区分マスタ'!$D$6,0)</f>
-        <v/>
-      </c>
-      <c r="E11" s="27">
-        <f>B11-C11-D11</f>
-        <v/>
-      </c>
-      <c r="F11" s="12">
-        <f>B11/B$7-1</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>推計</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>次期計画目標年度</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="B26" s="9" t="n">
+        <v>53877076</v>
+      </c>
+      <c r="C26" s="34" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>1635703</v>
+      </c>
+      <c r="E26" s="34" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="F26" s="8" t="inlineStr"/>
+      <c r="G26" s="8" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>介護の伸びは鈍化</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="50" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>介護給付費の前年度比は＋27.7％から−3.8％まで振れており、直近1年（＋2.2％）を将来4年に当てはめる根拠も、令和2〜7年度のCAGR（＋8.4％）を当てはめる根拠も、それぞれ単独では弱いものです。また、前回計画課題整理でも「1人の利用開始・終了で実績が大きく動くため、機械的な伸び率推計を避ける」ことを方針としています。本シートの2シナリオは、村の財政影響の幅を把握するための暫定的なものと位置づけ、サービス見込量が確定したら下表の積上げに置き換えてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>見込量×単価による積上げ（確定後に使用）</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>サービス</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>令和7年度
 月平均量</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>月額単価</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>令和9年度
 見込量</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>令和10年度
 見込量</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>令和11年度
 見込量</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>就労継続支援（B型）</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C31" s="35" t="n">
         <v>11.9</v>
       </c>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="30" t="n"/>
-      <c r="F15" s="30" t="n"/>
-      <c r="G15" s="30" t="n"/>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="D31" s="28" t="n"/>
+      <c r="E31" s="36" t="n"/>
+      <c r="F31" s="36" t="n"/>
+      <c r="G31" s="36" t="n"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>令和7年度 給付費19,707,121円。令和2年度比2.08倍の要因分析が必要</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>生活介護</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="C16" s="31" t="n">
+      <c r="C32" s="37" t="n">
         <v>6.6</v>
       </c>
-      <c r="D16" s="28" t="n"/>
-      <c r="E16" s="30" t="n"/>
-      <c r="F16" s="30" t="n"/>
-      <c r="G16" s="30" t="n"/>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="D32" s="28" t="n"/>
+      <c r="E32" s="36" t="n"/>
+      <c r="F32" s="36" t="n"/>
+      <c r="G32" s="36" t="n"/>
+      <c r="H32" s="8" t="inlineStr"/>
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>令和7年度 給付費13,209,810円</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>共同生活援助</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C33" s="35" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="D17" s="28" t="n"/>
-      <c r="E17" s="30" t="n"/>
-      <c r="F17" s="30" t="n"/>
-      <c r="G17" s="30" t="n"/>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="D33" s="28" t="n"/>
+      <c r="E33" s="36" t="n"/>
+      <c r="F33" s="36" t="n"/>
+      <c r="G33" s="36" t="n"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>令和7年度 給付費9,663,491円（特定障害者特別給付費を除く）</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>施設入所支援</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="C18" s="31" t="n">
+      <c r="C34" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="D18" s="28" t="n"/>
-      <c r="E18" s="30" t="n"/>
-      <c r="F18" s="30" t="n"/>
-      <c r="G18" s="30" t="n"/>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="D34" s="28" t="n"/>
+      <c r="E34" s="36" t="n"/>
+      <c r="F34" s="36" t="n"/>
+      <c r="G34" s="36" t="n"/>
+      <c r="H34" s="8" t="inlineStr"/>
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>4人で横ばい。成果目標と整合させる</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>計画相談支援</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C35" s="35" t="n">
         <v>6.3</v>
       </c>
-      <c r="D19" s="28" t="n"/>
-      <c r="E19" s="30" t="n"/>
-      <c r="F19" s="30" t="n"/>
-      <c r="G19" s="30" t="n"/>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="D35" s="28" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="36" t="n"/>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>令和7年度 給付費1,863,988円</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>居宅介護</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="C20" s="31" t="n">
+      <c r="C36" s="37" t="n">
         <v>3.7</v>
       </c>
-      <c r="D20" s="28" t="n"/>
-      <c r="E20" s="30" t="n"/>
-      <c r="F20" s="30" t="n"/>
-      <c r="G20" s="30" t="n"/>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="D36" s="28" t="n"/>
+      <c r="E36" s="36" t="n"/>
+      <c r="F36" s="36" t="n"/>
+      <c r="G36" s="36" t="n"/>
+      <c r="H36" s="8" t="inlineStr"/>
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>令和7年度 給付費1,713,336円</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>短期入所</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C37" s="35" t="n">
         <v>0.2</v>
       </c>
-      <c r="D21" s="28" t="n"/>
-      <c r="E21" s="30" t="n"/>
-      <c r="F21" s="30" t="n"/>
-      <c r="G21" s="30" t="n"/>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="D37" s="28" t="n"/>
+      <c r="E37" s="36" t="n"/>
+      <c r="F37" s="36" t="n"/>
+      <c r="G37" s="36" t="n"/>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>令和6年度から実績。令和9年度からの計上を検討</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>放課後等デイサービス</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="C22" s="31" t="n">
+      <c r="C38" s="37" t="n">
         <v>2.3</v>
       </c>
-      <c r="D22" s="28" t="n"/>
-      <c r="E22" s="30" t="n"/>
-      <c r="F22" s="30" t="n"/>
-      <c r="G22" s="30" t="n"/>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="36" t="n"/>
+      <c r="F38" s="36" t="n"/>
+      <c r="G38" s="36" t="n"/>
+      <c r="H38" s="8" t="inlineStr"/>
+      <c r="I38" s="8" t="inlineStr">
         <is>
           <t>令和7年度に件数27件へ増加</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>児童発達支援</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C39" s="35" t="n">
         <v>0.1</v>
       </c>
-      <c r="D23" s="28" t="n"/>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="30" t="n"/>
-      <c r="G23" s="30" t="n"/>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="D39" s="28" t="n"/>
+      <c r="E39" s="36" t="n"/>
+      <c r="F39" s="36" t="n"/>
+      <c r="G39" s="36" t="n"/>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>令和7年度は1件。対象児童の就学・通園状況を確認</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>保育所等訪問支援</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="C24" s="31" t="n">
+      <c r="C40" s="37" t="n">
         <v>0.3</v>
       </c>
-      <c r="D24" s="28" t="n"/>
-      <c r="E24" s="30" t="n"/>
-      <c r="F24" s="30" t="n"/>
-      <c r="G24" s="30" t="n"/>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="D40" s="28" t="n"/>
+      <c r="E40" s="36" t="n"/>
+      <c r="F40" s="36" t="n"/>
+      <c r="G40" s="36" t="n"/>
+      <c r="H40" s="8" t="inlineStr"/>
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>令和7年度に初めて実績が発生</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>障害児相談支援</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C41" s="35" t="n">
         <v>0.7</v>
       </c>
-      <c r="D25" s="28" t="n"/>
-      <c r="E25" s="30" t="n"/>
-      <c r="F25" s="30" t="n"/>
-      <c r="G25" s="30" t="n"/>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="D41" s="28" t="n"/>
+      <c r="E41" s="36" t="n"/>
+      <c r="F41" s="36" t="n"/>
+      <c r="G41" s="36" t="n"/>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>令和7年度 給付費330,460円</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>令和7年度の月平均量は、受領データの件数を12で除した参考値です（件数＝延べ利用月数と仮定）。実際の見込量は「人／月」「人日／月」「時間／月」など計画上の単位で設定する必要があるため、支給決定者数・実利用者数・利用日数の受領後に置き換えてください。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A27:H27"/>
+  <mergeCells count="8">
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/北塩原村_財源構成案.xlsx
+++ b/output/北塩原村_財源構成案.xlsx
@@ -27,8 +27,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="+0.0%;-0.0%"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="+0.0%;-0.0%"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -71,7 +71,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -128,11 +128,6 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3F3"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -160,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -246,28 +241,13 @@
     <xf numFmtId="3" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -874,11 +854,11 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>令和11年度 給付費推計（低位）</t>
+          <t>令和11年度 給付費推計（積上げ）</t>
         </is>
       </c>
       <c r="B12" s="9">
-        <f>'08_R9R11推計'!E16</f>
+        <f>'08_R9R11推計'!H23</f>
         <v/>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -886,93 +866,75 @@
           <t>08_R9R11推計</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>暫定</t>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>村資料待ち</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>介護給付費 年+2.2%（直近1年）シナリオ。見込量確定後に積上げへ置き換える</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>令和11年度 給付費推計（中位）</t>
-        </is>
-      </c>
-      <c r="B13" s="5">
-        <f>'08_R9R11推計'!F16</f>
-        <v/>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>08_R9R11推計</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>暫定</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>介護給付費 年+8.4%（令和2〜7年度CAGR）シナリオ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+          <t>サービス見込量ブックの個別積上げ×単価。見込量と単価の入力後に確定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>本ブックの使い方と留意点</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>1. 02・03シートの給付実績は受領データ（令和2〜7年度）の確定値です。原則として変更しません。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1. 02・03シートの給付実績は受領データ（令和2〜7年度）の確定値です。原則として変更しません。</t>
+          <t>2. 財源構成（04・05）は、01_負担区分マスタの負担割合を掛けた法定ベースの試算です。国庫負担基準額を超えた分は村負担となるため、実際の決算額とは一致しません。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2. 財源構成（04・05）は、01_負担区分マスタの負担割合を掛けた法定ベースの試算です。国庫負担基準額を超えた分は村負担となるため、実際の決算額とは一致しません。</t>
+          <t>3. 村の歳入歳出決算（障害者自立支援給付費負担金・障害児施設給付費負担金等）を受領したら、09_村確認事項の該当行を更新し、試算値と決算額の差を確認してください。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>3. 村の歳入歳出決算（障害者自立支援給付費負担金・障害児施設給付費負担金等）を受領したら、09_村確認事項の該当行を更新し、試算値と決算額の差を確認してください。</t>
+          <t>4. 地域生活支援事業（06）は国1/2以内・県1/4以内の統合補助金です。補助基準額を超える部分は全額村負担となるため、事業費・交付額・村負担を分けて把握する必要があります。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>4. 地域生活支援事業（06）は国1/2以内・県1/4以内の統合補助金です。補助基準額を超える部分は全額村負担となるため、事業費・交付額・村負担を分けて把握する必要があります。</t>
+          <t>5. 令和9〜11年度の給付費は、伸び率ではなく「北塩原村_サービス見込量.xlsx」の個別積上げ×単価で算定します。08シートに見込量と単価を入力してください。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>5. 計画書への掲載は、金額の羅列ではなく「総額の推移」「財源別構成比の推移」「サービス別の構成」の3点に絞ると読みやすくなります。</t>
+          <t>6. 計画書への掲載は、金額の羅列ではなく「総額の推移」「財源別構成比の推移」「サービス別の構成」の3点に絞ると読みやすくなります。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
   </mergeCells>
@@ -5026,15 +4988,15 @@
   <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -5047,956 +5009,961 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>給付費の年次変動が大きく、単一の伸び率では幅を表現できないため、低位・中位の2シナリオで示します。障害児給付費は対象児童の卒業・転入により大きく動くため、伸び率法を用いず令和7年度実績を横置きし、個別ケースによる増減を加算欄で調整します。サービス見込量が確定したら積上げに置き換えてください。単位：円。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>シナリオ設定（黄色セルが入力欄）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>低位シナリオ</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>中位シナリオ</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>根拠・考え方</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>介護給付費 年伸び率</t>
-        </is>
-      </c>
-      <c r="B6" s="29" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="C6" s="29" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>低位＝令和6→7年度の実績伸び率（＋2.2％）／中位＝令和2→7年度のCAGR（＋8.4％）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>障害児給付費</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>令和7年度実績を横置き</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>同左</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" s="8" t="inlineStr"/>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>令和4年度4,030千円→令和7年度1,636千円と3年で約6割減。対象児童の個別事情で動くため伸び率法は用いない</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>障害児給付費 個別加算（年額）</t>
-        </is>
-      </c>
-      <c r="B8" s="28" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>←低位・中位で共通</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>新規利用・卒業・転出入の見込みを金額で入力する（減額はマイナスで入力）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>給付費・財源構成の推計</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>年度</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>介護給付費
-低位</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>介護給付費
-中位</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>障害児
-給付費</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>計
-低位</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>計
-中位</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>村負担
-低位</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>村負担
-中位</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>区分・備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>令和7年度</t>
-        </is>
-      </c>
-      <c r="B12" s="27">
-        <f>'02_給付実績_介護給付費'!H20</f>
-        <v/>
-      </c>
-      <c r="C12" s="27">
-        <f>B12</f>
-        <v/>
-      </c>
-      <c r="D12" s="27">
-        <f>'03_給付実績_障害児給付費'!H10</f>
-        <v/>
-      </c>
-      <c r="E12" s="27">
-        <f>B12+D12</f>
-        <v/>
-      </c>
-      <c r="F12" s="27">
-        <f>C12+D12</f>
-        <v/>
-      </c>
-      <c r="G12" s="27">
-        <f>ROUND(E12*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
-        <v/>
-      </c>
-      <c r="H12" s="27">
-        <f>ROUND(F12*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
-        <v/>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>実績／受領データによる確定値</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>令和8年度</t>
-        </is>
-      </c>
-      <c r="B13" s="27">
-        <f>ROUND(B12*(1+$B$6),0)</f>
-        <v/>
-      </c>
-      <c r="C13" s="27">
-        <f>ROUND(C12*(1+$C$6),0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="27">
-        <f>D12+N($B$8)</f>
-        <v/>
-      </c>
-      <c r="E13" s="27">
-        <f>B13+D13</f>
-        <v/>
-      </c>
-      <c r="F13" s="27">
-        <f>C13+D13</f>
-        <v/>
-      </c>
-      <c r="G13" s="27">
-        <f>ROUND(E13*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
-        <v/>
-      </c>
-      <c r="H13" s="27">
-        <f>ROUND(F13*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
-        <v/>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>見込／現行計画最終年度。村の最新見込を受領したら実額に差し替える</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="B14" s="27">
-        <f>ROUND(B13*(1+$B$6),0)</f>
-        <v/>
-      </c>
-      <c r="C14" s="27">
-        <f>ROUND(C13*(1+$C$6),0)</f>
-        <v/>
-      </c>
-      <c r="D14" s="27">
-        <f>D12+N($B$8)</f>
-        <v/>
-      </c>
-      <c r="E14" s="27">
-        <f>B14+D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="27">
-        <f>C14+D14</f>
-        <v/>
-      </c>
-      <c r="G14" s="27">
-        <f>ROUND(E14*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
-        <v/>
-      </c>
-      <c r="H14" s="27">
-        <f>ROUND(F14*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
-        <v/>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>推計／次期計画1年目</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>令和10年度</t>
-        </is>
-      </c>
-      <c r="B15" s="27">
-        <f>ROUND(B14*(1+$B$6),0)</f>
-        <v/>
-      </c>
-      <c r="C15" s="27">
-        <f>ROUND(C14*(1+$C$6),0)</f>
-        <v/>
-      </c>
-      <c r="D15" s="27">
-        <f>D12+N($B$8)</f>
-        <v/>
-      </c>
-      <c r="E15" s="27">
-        <f>B15+D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="27">
-        <f>C15+D15</f>
-        <v/>
-      </c>
-      <c r="G15" s="27">
-        <f>ROUND(E15*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
-        <v/>
-      </c>
-      <c r="H15" s="27">
-        <f>ROUND(F15*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
-        <v/>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>推計／次期計画2年目</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="B16" s="27">
-        <f>ROUND(B15*(1+$B$6),0)</f>
-        <v/>
-      </c>
-      <c r="C16" s="27">
-        <f>ROUND(C15*(1+$C$6),0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="27">
-        <f>D12+N($B$8)</f>
-        <v/>
-      </c>
-      <c r="E16" s="27">
-        <f>B16+D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="27">
-        <f>C16+D16</f>
-        <v/>
-      </c>
-      <c r="G16" s="27">
-        <f>ROUND(E16*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
-        <v/>
-      </c>
-      <c r="H16" s="27">
-        <f>ROUND(F16*(1-'01_負担区分マスタ'!$C$6-'01_負担区分マスタ'!$D$6),0)</f>
-        <v/>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>推計／次期計画目標年度</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>低位と中位の差</t>
-        </is>
-      </c>
-      <c r="B17" s="31" t="inlineStr"/>
-      <c r="C17" s="31" t="inlineStr"/>
-      <c r="D17" s="31" t="inlineStr"/>
-      <c r="E17" s="31">
-        <f>F16-E16</f>
-        <v/>
-      </c>
-      <c r="F17" s="31" t="inlineStr"/>
-      <c r="G17" s="31">
-        <f>H16-G16</f>
-        <v/>
-      </c>
-      <c r="H17" s="31" t="inlineStr"/>
-      <c r="I17" s="32" t="inlineStr">
-        <is>
-          <t>令和11年度における両シナリオの差（左：給付費／右：村負担）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>伸び率を単一値で置けない理由（実績の年次変動）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>年度</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>介護給付費</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>前年度比</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>障害児給付費</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>前年度比</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>令和2年度</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>36002274</v>
-      </c>
-      <c r="C21" s="33" t="n"/>
-      <c r="D21" s="5" t="n">
-        <v>746064</v>
-      </c>
-      <c r="E21" s="33" t="n"/>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>基準年度</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>令和3年度</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="n">
-        <v>45991635</v>
-      </c>
-      <c r="C22" s="34" t="n">
-        <v>0.277</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>3254621</v>
-      </c>
-      <c r="E22" s="34" t="n">
-        <v>3.362</v>
-      </c>
-      <c r="F22" s="8" t="inlineStr"/>
-      <c r="G22" s="8" t="inlineStr"/>
-      <c r="H22" s="8" t="inlineStr"/>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>共同生活援助・就労継続支援B型の増</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>令和4年度</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>44234021</v>
-      </c>
-      <c r="C23" s="33" t="n">
-        <v>-0.038</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>4030423</v>
-      </c>
-      <c r="E23" s="33" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>障害児給付費のピーク</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>令和5年度</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n">
-        <v>44419974</v>
-      </c>
-      <c r="C24" s="34" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>3577832</v>
-      </c>
-      <c r="E24" s="34" t="n">
-        <v>-0.112</v>
-      </c>
-      <c r="F24" s="8" t="inlineStr"/>
-      <c r="G24" s="8" t="inlineStr"/>
-      <c r="H24" s="8" t="inlineStr"/>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>ほぼ横ばい</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>52698808</v>
-      </c>
-      <c r="C25" s="33" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>1641275</v>
-      </c>
-      <c r="E25" s="33" t="n">
-        <v>-0.541</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr"/>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>介護は大幅増、障害児は大幅減</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>令和7年度</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="n">
-        <v>53877076</v>
-      </c>
-      <c r="C26" s="34" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="D26" s="9" t="n">
-        <v>1635703</v>
-      </c>
-      <c r="E26" s="34" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="F26" s="8" t="inlineStr"/>
-      <c r="G26" s="8" t="inlineStr"/>
-      <c r="H26" s="8" t="inlineStr"/>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>介護の伸びは鈍化</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="50" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>介護給付費の前年度比は＋27.7％から−3.8％まで振れており、直近1年（＋2.2％）を将来4年に当てはめる根拠も、令和2〜7年度のCAGR（＋8.4％）を当てはめる根拠も、それぞれ単独では弱いものです。また、前回計画課題整理でも「1人の利用開始・終了で実績が大きく動くため、機械的な伸び率推計を避ける」ことを方針としています。本シートの2シナリオは、村の財政影響の幅を把握するための暫定的なものと位置づけ、サービス見込量が確定したら下表の積上げに置き換えてください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>見込量×単価による積上げ（確定後に使用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+          <t>給付費は「サービス見込量ブック（北塩原村_サービス見込量.xlsx）の個別積上げ × 単価」で算定します。伸び率による推計は、未特定の潜在需要（第3層）を補正する場合に限って用います。本村では利用者1人の増減が生活介護で16.7%、居宅介護・施設入所支援で25%を占め、年率2〜8%の伸び率を大きく上回るためです。単位：円。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>1. サービス別の積上げ（見込量×単価）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>サービス</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>令和7年度
-月平均量</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>月額単価</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>令和8年度
+見込量</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>令和9年度
 見込量</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>令和10年度
 見込量</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>令和11年度
 見込量</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr"/>
-      <c r="I30" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>令和11年度
+年間給付費</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>生活介護</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>人日／月</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="n"/>
+      <c r="D7" s="29" t="n"/>
+      <c r="E7" s="29" t="n"/>
+      <c r="F7" s="29" t="n"/>
+      <c r="G7" s="29" t="n"/>
+      <c r="H7" s="27">
+        <f>IFERROR(ROUND(C7*G7*12,0),"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度 給付費13,209,810円。特別支援学校卒業者の主な移行先</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>就労継続支援（B型）</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>人日／月</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="n"/>
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="29" t="n"/>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
+      <c r="H8" s="27">
+        <f>IFERROR(ROUND(C8*G8*12,0),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>令和7年度 給付費19,707,121円。令和2年度比2.08倍の要因分析が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>共同生活援助</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="n"/>
+      <c r="D9" s="29" t="n"/>
+      <c r="E9" s="29" t="n"/>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="29" t="n"/>
+      <c r="H9" s="27">
+        <f>IFERROR(ROUND(C9*G9*12,0),"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>介護保険に相当サービスがなく、65歳以降も継続する</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>施設入所支援</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C10" s="28" t="n"/>
+      <c r="D10" s="29" t="n"/>
+      <c r="E10" s="29" t="n"/>
+      <c r="F10" s="29" t="n"/>
+      <c r="G10" s="29" t="n"/>
+      <c r="H10" s="27">
+        <f>IFERROR(ROUND(C10*G10*12,0),"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>介護保険に相当サービスなし。成果目標（１）と整合させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>居宅介護</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>時間／月</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="29" t="n"/>
+      <c r="F11" s="29" t="n"/>
+      <c r="G11" s="29" t="n"/>
+      <c r="H11" s="27">
+        <f>IFERROR(ROUND(C11*G11*12,0),"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>介護保険の訪問介護に相当。65歳到達者は個別に判定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>計画相談支援</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="29" t="n"/>
+      <c r="E12" s="29" t="n"/>
+      <c r="F12" s="29" t="n"/>
+      <c r="G12" s="29" t="n"/>
+      <c r="H12" s="27">
+        <f>IFERROR(ROUND(C12*G12*12,0),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>請求は計画作成・モニタリング時のみ。実利用者数と請求件数は異なる</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>短期入所</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>人日／月</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="29" t="n"/>
+      <c r="E13" s="29" t="n"/>
+      <c r="F13" s="29" t="n"/>
+      <c r="G13" s="29" t="n"/>
+      <c r="H13" s="27">
+        <f>IFERROR(ROUND(C13*G13*12,0),"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>令和6年度2件・令和7年度3件の実績。令和9年度からの計上を検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>自立訓練（生活訓練）</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>人日／月</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="29" t="n"/>
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="29" t="n"/>
+      <c r="G14" s="29" t="n"/>
+      <c r="H14" s="27">
+        <f>IFERROR(ROUND(C14*G14*12,0),"")</f>
+        <v/>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>令和7年度 給付費382,238円</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>就労移行支援</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>人日／月</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="29" t="n"/>
+      <c r="F15" s="29" t="n"/>
+      <c r="G15" s="29" t="n"/>
+      <c r="H15" s="27">
+        <f>IFERROR(ROUND(C15*G15*12,0),"")</f>
+        <v/>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>一般就労移行の成果目標と連動</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>就労継続支援（A型）</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>人日／月</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="29" t="n"/>
+      <c r="E16" s="29" t="n"/>
+      <c r="F16" s="29" t="n"/>
+      <c r="G16" s="29" t="n"/>
+      <c r="H16" s="27">
+        <f>IFERROR(ROUND(C16*G16*12,0),"")</f>
+        <v/>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>現利用者への継続提供</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>就労定着支援</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="29" t="n"/>
+      <c r="G17" s="29" t="n"/>
+      <c r="H17" s="27">
+        <f>IFERROR(ROUND(C17*G17*12,0),"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>一般就労移行者数と連動</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>就労選択支援</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="29" t="n"/>
+      <c r="G18" s="29" t="n"/>
+      <c r="H18" s="27">
+        <f>IFERROR(ROUND(C18*G18*12,0),"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>令和7年10月開始。圏域事業所の有無を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>児童発達支援</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>人日／月</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="29" t="n"/>
+      <c r="G19" s="29" t="n"/>
+      <c r="H19" s="27">
+        <f>IFERROR(ROUND(C19*G19*12,0),"")</f>
+        <v/>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度は請求1件。就学に伴う移行の可能性（要確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>放課後等デイサービス</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>人日／月</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="n"/>
+      <c r="D20" s="29" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="29" t="n"/>
+      <c r="G20" s="29" t="n"/>
+      <c r="H20" s="27">
+        <f>IFERROR(ROUND(C20*G20*12,0),"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>令和7年度は請求27件。就学に伴う流入の可能性（要確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>保育所等訪問支援</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="29" t="n"/>
+      <c r="F21" s="29" t="n"/>
+      <c r="G21" s="29" t="n"/>
+      <c r="H21" s="27">
+        <f>IFERROR(ROUND(C21*G21*12,0),"")</f>
+        <v/>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度に初めて実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>障がい児相談支援</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="29" t="n"/>
+      <c r="F22" s="29" t="n"/>
+      <c r="G22" s="29" t="n"/>
+      <c r="H22" s="27">
+        <f>IFERROR(ROUND(C22*G22*12,0),"")</f>
+        <v/>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>令和7年度 給付費330,460円</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H23" s="22">
+        <f>SUM(H7:H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>積上げによる令和11年度の年間給付費</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>見込量は「北塩原村_サービス見込量.xlsx」の03・04シートの『月間サービス量』を転記します。単価は直近の実績単価（令和7年度の給付費÷利用量）を基本とし、報酬改定が見込まれる場合は補正します。外部リンクにするとファイル移動時に壊れるため、転記は手作業としています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>2. 財源構成</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>自立支援給付計</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>国庫負担</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>県負担</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>村負担</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>対令和7年度</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>区分・備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="27">
+        <f>'04_財源構成試算'!D11</f>
+        <v/>
+      </c>
+      <c r="E28" s="27">
+        <f>IFERROR(ROUND(D28*'01_負担区分マスタ'!$C$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="27">
+        <f>IFERROR(ROUND(D28*'01_負担区分マスタ'!$D$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="27">
+        <f>IFERROR(D28-E28-F28,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="30">
+        <f>IFERROR(D28/D$28-1,"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>実績／受領データによる確定値</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr"/>
+      <c r="C29" s="8" t="inlineStr"/>
+      <c r="D29" s="28" t="n"/>
+      <c r="E29" s="27">
+        <f>IFERROR(ROUND(D29*'01_負担区分マスタ'!$C$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="27">
+        <f>IFERROR(ROUND(D29*'01_負担区分マスタ'!$D$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="27">
+        <f>IFERROR(D29-E29-F29,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="30">
+        <f>IFERROR(D29/D$28-1,"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>見込／村の最新見込を受領して入力する</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr"/>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="28" t="n"/>
+      <c r="E30" s="27">
+        <f>IFERROR(ROUND(D30*'01_負担区分マスタ'!$C$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="27">
+        <f>IFERROR(ROUND(D30*'01_負担区分マスタ'!$D$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="27">
+        <f>IFERROR(D30-E30-F30,"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="30">
+        <f>IFERROR(D30/D$28-1,"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>推計／積上げ結果を入力する（次期計画1年目）</t>
+        </is>
+      </c>
+    </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>就労継続支援（B型）</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C31" s="35" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr"/>
+      <c r="C31" s="8" t="inlineStr"/>
       <c r="D31" s="28" t="n"/>
-      <c r="E31" s="36" t="n"/>
-      <c r="F31" s="36" t="n"/>
-      <c r="G31" s="36" t="n"/>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度 給付費19,707,121円。令和2年度比2.08倍の要因分析が必要</t>
+      <c r="E31" s="27">
+        <f>IFERROR(ROUND(D31*'01_負担区分マスタ'!$C$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="27">
+        <f>IFERROR(ROUND(D31*'01_負担区分マスタ'!$D$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="27">
+        <f>IFERROR(D31-E31-F31,"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="30">
+        <f>IFERROR(D31/D$28-1,"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>推計／積上げ結果を入力する（次期計画2年目）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>生活介護</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C32" s="37" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="D32" s="28" t="n"/>
-      <c r="E32" s="36" t="n"/>
-      <c r="F32" s="36" t="n"/>
-      <c r="G32" s="36" t="n"/>
-      <c r="H32" s="8" t="inlineStr"/>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>令和7年度 給付費13,209,810円</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>共同生活援助</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C33" s="35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="D33" s="28" t="n"/>
-      <c r="E33" s="36" t="n"/>
-      <c r="F33" s="36" t="n"/>
-      <c r="G33" s="36" t="n"/>
-      <c r="H33" s="4" t="inlineStr"/>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度 給付費9,663,491円（特定障害者特別給付費を除く）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>施設入所支援</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C34" s="37" t="n">
-        <v>4</v>
-      </c>
-      <c r="D34" s="28" t="n"/>
-      <c r="E34" s="36" t="n"/>
-      <c r="F34" s="36" t="n"/>
-      <c r="G34" s="36" t="n"/>
-      <c r="H34" s="8" t="inlineStr"/>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t>4人で横ばい。成果目標と整合させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>計画相談支援</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C35" s="35" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="D35" s="28" t="n"/>
-      <c r="E35" s="36" t="n"/>
-      <c r="F35" s="36" t="n"/>
-      <c r="G35" s="36" t="n"/>
-      <c r="H35" s="4" t="inlineStr"/>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度 給付費1,863,988円</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>居宅介護</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C36" s="37" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D36" s="28" t="n"/>
-      <c r="E36" s="36" t="n"/>
-      <c r="F36" s="36" t="n"/>
-      <c r="G36" s="36" t="n"/>
-      <c r="H36" s="8" t="inlineStr"/>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>令和7年度 給付費1,713,336円</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>短期入所</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C37" s="35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D37" s="28" t="n"/>
-      <c r="E37" s="36" t="n"/>
-      <c r="F37" s="36" t="n"/>
-      <c r="G37" s="36" t="n"/>
-      <c r="H37" s="4" t="inlineStr"/>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>令和6年度から実績。令和9年度からの計上を検討</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>放課後等デイサービス</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C38" s="37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="D38" s="28" t="n"/>
-      <c r="E38" s="36" t="n"/>
-      <c r="F38" s="36" t="n"/>
-      <c r="G38" s="36" t="n"/>
-      <c r="H38" s="8" t="inlineStr"/>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>令和7年度に件数27件へ増加</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>児童発達支援</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C39" s="35" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D39" s="28" t="n"/>
-      <c r="E39" s="36" t="n"/>
-      <c r="F39" s="36" t="n"/>
-      <c r="G39" s="36" t="n"/>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度は1件。対象児童の就学・通園状況を確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>保育所等訪問支援</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C40" s="37" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D40" s="28" t="n"/>
-      <c r="E40" s="36" t="n"/>
-      <c r="F40" s="36" t="n"/>
-      <c r="G40" s="36" t="n"/>
-      <c r="H40" s="8" t="inlineStr"/>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>令和7年度に初めて実績が発生</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>障害児相談支援</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C41" s="35" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D41" s="28" t="n"/>
-      <c r="E41" s="36" t="n"/>
-      <c r="F41" s="36" t="n"/>
-      <c r="G41" s="36" t="n"/>
-      <c r="H41" s="4" t="inlineStr"/>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度 給付費330,460円</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="34" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr"/>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="27">
+        <f>H23</f>
+        <v/>
+      </c>
+      <c r="E32" s="27">
+        <f>IFERROR(ROUND(D32*'01_負担区分マスタ'!$C$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="27">
+        <f>IFERROR(ROUND(D32*'01_負担区分マスタ'!$D$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="27">
+        <f>IFERROR(D32-E32-F32,"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="30">
+        <f>IFERROR(D32/D$28-1,"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>推計／上表の積上げ合計を自動参照（目標年度）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>3. 参考：伸び率による推計（第3層の補正にのみ用いる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>介護給付費</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>前年度比</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>障害児給付費</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>前年度比</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>令和2年度</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>36002274</v>
+      </c>
+      <c r="C36" s="31" t="n"/>
+      <c r="D36" s="5" t="n">
+        <v>746064</v>
+      </c>
+      <c r="E36" s="31" t="n"/>
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>基準年度</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>令和3年度</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n">
+        <v>45991635</v>
+      </c>
+      <c r="C37" s="32" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>3254621</v>
+      </c>
+      <c r="E37" s="32" t="n">
+        <v>3.362</v>
+      </c>
+      <c r="F37" s="8" t="inlineStr"/>
+      <c r="G37" s="8" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>共同生活援助・就労継続支援B型の増</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>令和4年度</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>44234021</v>
+      </c>
+      <c r="C38" s="31" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>4030423</v>
+      </c>
+      <c r="E38" s="31" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>障害児給付費のピーク</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>令和5年度</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>44419974</v>
+      </c>
+      <c r="C39" s="32" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>3577832</v>
+      </c>
+      <c r="E39" s="32" t="n">
+        <v>-0.112</v>
+      </c>
+      <c r="F39" s="8" t="inlineStr"/>
+      <c r="G39" s="8" t="inlineStr"/>
+      <c r="H39" s="8" t="inlineStr"/>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>ほぼ横ばい</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>52698808</v>
+      </c>
+      <c r="C40" s="31" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>1641275</v>
+      </c>
+      <c r="E40" s="31" t="n">
+        <v>-0.541</v>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>介護は大幅増。障害児の減は就学移行の可能性</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>53877076</v>
+      </c>
+      <c r="C41" s="32" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>1635703</v>
+      </c>
+      <c r="E41" s="32" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="F41" s="8" t="inlineStr"/>
+      <c r="G41" s="8" t="inlineStr"/>
+      <c r="H41" s="8" t="inlineStr"/>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>介護の伸びは鈍化</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="62" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>令和7年度の月平均量は、受領データの件数を12で除した参考値です（件数＝延べ利用月数と仮定）。実際の見込量は「人／月」「人日／月」「時間／月」など計画上の単位で設定する必要があるため、支給決定者数・実利用者数・利用日数の受領後に置き換えてください。</t>
+          <t>介護給付費の前年度比は＋27.7％から−3.8％まで振れており、令和2〜7年度のCAGRは＋8.4％、直近1年は＋2.2％です。いずれも単一値として将来4年に当てはめる根拠は弱く、本表は伸び率の不安定さを示す参考資料として置いています。障害児給付費の減少は、令和6・7年度に児童発達支援が減り放課後等デイサービスが増えていることから、対象児童の就学に伴う移行である可能性があります（受給者単位の確認が必要）。ニーズの減少と断定しないでください。前回計画課題整理でも「1人の利用開始・終了で実績が大きく動くため、機械的な伸び率推計を避ける」ことを方針としています。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A19:I19"/>
+  <mergeCells count="7">
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A5:I5"/>
     <mergeCell ref="A42:I42"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A24:I24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/北塩原村_財源構成案.xlsx
+++ b/output/北塩原村_財源構成案.xlsx
@@ -25,10 +25,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="+0.0%;-0.0%"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -129,7 +130,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -151,11 +152,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -244,13 +289,27 @@
     <xf numFmtId="165" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -858,7 +917,7 @@
         </is>
       </c>
       <c r="B12" s="9">
-        <f>'08_R9R11推計'!H23</f>
+        <f>'08_R9R11推計'!H29</f>
         <v/>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -4985,7 +5044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5016,222 +5075,176 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>1. サービス別の積上げ（見込量×単価）</t>
+          <t>1. 報酬改定の前提（単価の補正率）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>改定率</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>施行</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>令和8年度報酬改定</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>令和8年6月1日</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>①福祉・介護職員等処遇改善加算の拡充（対象を障害福祉従事者へ拡大。月1.0万円＝3.3％の賃上げ、生産性向上・協働化に取り組む事業者は月0.3万円＝1.0％を上乗せ。計画相談支援・障害児相談支援・地域相談支援に新設）②就労継続支援B型の基本報酬区分の基準見直し ③新規指定事業所に限る応急的な報酬単価（B型 所定単位数の984/1000、共同生活援助（介護サービス包括型・日中サービス支援型）972/1000 ほか児童発達支援・放課後等デイサービス）</t>
+        </is>
+      </c>
+      <c r="E7" s="30" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
+      <c r="H7" s="30" t="n"/>
+      <c r="I7" s="31" t="n"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>令和9年度報酬改定</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>令和9年4月（予定）</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>次期計画期間の初年度に当たる。令和8年度改定の応急的単価が「令和9年度報酬改定までの間」とされていることから実施が見込まれる。内容確定後に改定率を入力する</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
+      <c r="H8" s="30" t="n"/>
+      <c r="I8" s="31" t="n"/>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>適用倍率（合計）</t>
+        </is>
+      </c>
+      <c r="B9" s="32">
+        <f>B7*B8</f>
+        <v/>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D9" s="34" t="inlineStr">
+        <is>
+          <t>下表の令和11年度年間給付費に乗じます。改定率が確定するまでは1.000（改定なし）として計算します。離島・中山間地域（特別地域加算の対象地域）の事業所や重度障がい者に係る基本報酬には従前単価が適用される配慮措置があるため、圏域事業所の該当状況を確認してください。</t>
+        </is>
+      </c>
+      <c r="E9" s="30" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
+      <c r="H9" s="30" t="n"/>
+      <c r="I9" s="31" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>2. サービス別の積上げ（見込量×単価）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>サービス</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>月額単価</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>令和8年度
 見込量</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>令和9年度
 見込量</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>令和10年度
 見込量</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>令和11年度
 見込量</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>令和11年度
 年間給付費</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>生活介護</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>人日／月</t>
-        </is>
-      </c>
-      <c r="C7" s="28" t="n"/>
-      <c r="D7" s="29" t="n"/>
-      <c r="E7" s="29" t="n"/>
-      <c r="F7" s="29" t="n"/>
-      <c r="G7" s="29" t="n"/>
-      <c r="H7" s="27">
-        <f>IFERROR(ROUND(C7*G7*12,0),"")</f>
-        <v/>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>令和7年度 給付費13,209,810円。特別支援学校卒業者の主な移行先</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>就労継続支援（B型）</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>人日／月</t>
-        </is>
-      </c>
-      <c r="C8" s="28" t="n"/>
-      <c r="D8" s="29" t="n"/>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="29" t="n"/>
-      <c r="H8" s="27">
-        <f>IFERROR(ROUND(C8*G8*12,0),"")</f>
-        <v/>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>令和7年度 給付費19,707,121円。令和2年度比2.08倍の要因分析が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>共同生活援助</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C9" s="28" t="n"/>
-      <c r="D9" s="29" t="n"/>
-      <c r="E9" s="29" t="n"/>
-      <c r="F9" s="29" t="n"/>
-      <c r="G9" s="29" t="n"/>
-      <c r="H9" s="27">
-        <f>IFERROR(ROUND(C9*G9*12,0),"")</f>
-        <v/>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>介護保険に相当サービスがなく、65歳以降も継続する</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>施設入所支援</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C10" s="28" t="n"/>
-      <c r="D10" s="29" t="n"/>
-      <c r="E10" s="29" t="n"/>
-      <c r="F10" s="29" t="n"/>
-      <c r="G10" s="29" t="n"/>
-      <c r="H10" s="27">
-        <f>IFERROR(ROUND(C10*G10*12,0),"")</f>
-        <v/>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>介護保険に相当サービスなし。成果目標（１）と整合させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>居宅介護</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>時間／月</t>
-        </is>
-      </c>
-      <c r="C11" s="28" t="n"/>
-      <c r="D11" s="29" t="n"/>
-      <c r="E11" s="29" t="n"/>
-      <c r="F11" s="29" t="n"/>
-      <c r="G11" s="29" t="n"/>
-      <c r="H11" s="27">
-        <f>IFERROR(ROUND(C11*G11*12,0),"")</f>
-        <v/>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>介護保険の訪問介護に相当。65歳到達者は個別に判定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>計画相談支援</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>人／月</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="n"/>
-      <c r="D12" s="29" t="n"/>
-      <c r="E12" s="29" t="n"/>
-      <c r="F12" s="29" t="n"/>
-      <c r="G12" s="29" t="n"/>
-      <c r="H12" s="27">
-        <f>IFERROR(ROUND(C12*G12*12,0),"")</f>
-        <v/>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>請求は計画作成・モニタリング時のみ。実利用者数と請求件数は異なる</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>短期入所</t>
+          <t>生活介護</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -5240,24 +5253,24 @@
         </is>
       </c>
       <c r="C13" s="28" t="n"/>
-      <c r="D13" s="29" t="n"/>
-      <c r="E13" s="29" t="n"/>
-      <c r="F13" s="29" t="n"/>
-      <c r="G13" s="29" t="n"/>
+      <c r="D13" s="35" t="n"/>
+      <c r="E13" s="35" t="n"/>
+      <c r="F13" s="35" t="n"/>
+      <c r="G13" s="35" t="n"/>
       <c r="H13" s="27">
-        <f>IFERROR(ROUND(C13*G13*12,0),"")</f>
+        <f>IFERROR(ROUND(C13*G13*12*$B$9,0),"")</f>
         <v/>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>令和6年度2件・令和7年度3件の実績。令和9年度からの計上を検討</t>
+          <t>令和7年度 給付費13,209,810円。特別支援学校卒業者の主な移行先</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>自立訓練（生活訓練）</t>
+          <t>就労継続支援（B型）</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -5266,102 +5279,102 @@
         </is>
       </c>
       <c r="C14" s="28" t="n"/>
-      <c r="D14" s="29" t="n"/>
-      <c r="E14" s="29" t="n"/>
-      <c r="F14" s="29" t="n"/>
-      <c r="G14" s="29" t="n"/>
+      <c r="D14" s="35" t="n"/>
+      <c r="E14" s="35" t="n"/>
+      <c r="F14" s="35" t="n"/>
+      <c r="G14" s="35" t="n"/>
       <c r="H14" s="27">
-        <f>IFERROR(ROUND(C14*G14*12,0),"")</f>
+        <f>IFERROR(ROUND(C14*G14*12*$B$9,0),"")</f>
         <v/>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>令和7年度 給付費382,238円</t>
+          <t>令和7年度 給付費19,707,121円。令和2年度比2.08倍の要因分析が必要</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>就労移行支援</t>
+          <t>共同生活援助</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>人日／月</t>
+          <t>人／月</t>
         </is>
       </c>
       <c r="C15" s="28" t="n"/>
-      <c r="D15" s="29" t="n"/>
-      <c r="E15" s="29" t="n"/>
-      <c r="F15" s="29" t="n"/>
-      <c r="G15" s="29" t="n"/>
+      <c r="D15" s="35" t="n"/>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
+      <c r="G15" s="35" t="n"/>
       <c r="H15" s="27">
-        <f>IFERROR(ROUND(C15*G15*12,0),"")</f>
+        <f>IFERROR(ROUND(C15*G15*12*$B$9,0),"")</f>
         <v/>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>一般就労移行の成果目標と連動</t>
+          <t>介護保険に相当サービスがなく、65歳以降も継続する</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>就労継続支援（A型）</t>
+          <t>施設入所支援</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>人日／月</t>
+          <t>人／月</t>
         </is>
       </c>
       <c r="C16" s="28" t="n"/>
-      <c r="D16" s="29" t="n"/>
-      <c r="E16" s="29" t="n"/>
-      <c r="F16" s="29" t="n"/>
-      <c r="G16" s="29" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n"/>
+      <c r="F16" s="35" t="n"/>
+      <c r="G16" s="35" t="n"/>
       <c r="H16" s="27">
-        <f>IFERROR(ROUND(C16*G16*12,0),"")</f>
+        <f>IFERROR(ROUND(C16*G16*12*$B$9,0),"")</f>
         <v/>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>現利用者への継続提供</t>
+          <t>介護保険に相当サービスなし。成果目標（１）と整合させる</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>就労定着支援</t>
+          <t>居宅介護</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>人／月</t>
+          <t>時間／月</t>
         </is>
       </c>
       <c r="C17" s="28" t="n"/>
-      <c r="D17" s="29" t="n"/>
-      <c r="E17" s="29" t="n"/>
-      <c r="F17" s="29" t="n"/>
-      <c r="G17" s="29" t="n"/>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="35" t="n"/>
       <c r="H17" s="27">
-        <f>IFERROR(ROUND(C17*G17*12,0),"")</f>
+        <f>IFERROR(ROUND(C17*G17*12*$B$9,0),"")</f>
         <v/>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>一般就労移行者数と連動</t>
+          <t>介護保険の訪問介護に相当。65歳到達者は個別に判定する</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>就労選択支援</t>
+          <t>計画相談支援</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -5370,24 +5383,24 @@
         </is>
       </c>
       <c r="C18" s="28" t="n"/>
-      <c r="D18" s="29" t="n"/>
-      <c r="E18" s="29" t="n"/>
-      <c r="F18" s="29" t="n"/>
-      <c r="G18" s="29" t="n"/>
+      <c r="D18" s="35" t="n"/>
+      <c r="E18" s="35" t="n"/>
+      <c r="F18" s="35" t="n"/>
+      <c r="G18" s="35" t="n"/>
       <c r="H18" s="27">
-        <f>IFERROR(ROUND(C18*G18*12,0),"")</f>
+        <f>IFERROR(ROUND(C18*G18*12*$B$9,0),"")</f>
         <v/>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>令和7年10月開始。圏域事業所の有無を確認</t>
+          <t>請求は計画作成・モニタリング時のみ。実利用者数と請求件数は異なる</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>児童発達支援</t>
+          <t>短期入所</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -5396,24 +5409,24 @@
         </is>
       </c>
       <c r="C19" s="28" t="n"/>
-      <c r="D19" s="29" t="n"/>
-      <c r="E19" s="29" t="n"/>
-      <c r="F19" s="29" t="n"/>
-      <c r="G19" s="29" t="n"/>
+      <c r="D19" s="35" t="n"/>
+      <c r="E19" s="35" t="n"/>
+      <c r="F19" s="35" t="n"/>
+      <c r="G19" s="35" t="n"/>
       <c r="H19" s="27">
-        <f>IFERROR(ROUND(C19*G19*12,0),"")</f>
+        <f>IFERROR(ROUND(C19*G19*12*$B$9,0),"")</f>
         <v/>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>令和7年度は請求1件。就学に伴う移行の可能性（要確認）</t>
+          <t>令和6年度2件・令和7年度3件の実績。令和9年度からの計上を検討</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>放課後等デイサービス</t>
+          <t>自立訓練（生活訓練）</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -5422,548 +5435,708 @@
         </is>
       </c>
       <c r="C20" s="28" t="n"/>
-      <c r="D20" s="29" t="n"/>
-      <c r="E20" s="29" t="n"/>
-      <c r="F20" s="29" t="n"/>
-      <c r="G20" s="29" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="35" t="n"/>
+      <c r="G20" s="35" t="n"/>
       <c r="H20" s="27">
-        <f>IFERROR(ROUND(C20*G20*12,0),"")</f>
+        <f>IFERROR(ROUND(C20*G20*12*$B$9,0),"")</f>
         <v/>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>令和7年度は請求27件。就学に伴う流入の可能性（要確認）</t>
+          <t>令和7年度 給付費382,238円</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>保育所等訪問支援</t>
+          <t>就労移行支援</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>人／月</t>
+          <t>人日／月</t>
         </is>
       </c>
       <c r="C21" s="28" t="n"/>
-      <c r="D21" s="29" t="n"/>
-      <c r="E21" s="29" t="n"/>
-      <c r="F21" s="29" t="n"/>
-      <c r="G21" s="29" t="n"/>
+      <c r="D21" s="35" t="n"/>
+      <c r="E21" s="35" t="n"/>
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="35" t="n"/>
       <c r="H21" s="27">
-        <f>IFERROR(ROUND(C21*G21*12,0),"")</f>
+        <f>IFERROR(ROUND(C21*G21*12*$B$9,0),"")</f>
         <v/>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>令和7年度に初めて実績</t>
+          <t>一般就労移行の成果目標と連動</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>就労継続支援（A型）</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>人日／月</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="35" t="n"/>
+      <c r="E22" s="35" t="n"/>
+      <c r="F22" s="35" t="n"/>
+      <c r="G22" s="35" t="n"/>
+      <c r="H22" s="27">
+        <f>IFERROR(ROUND(C22*G22*12*$B$9,0),"")</f>
+        <v/>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>現利用者への継続提供</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>就労定着支援</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="35" t="n"/>
+      <c r="F23" s="35" t="n"/>
+      <c r="G23" s="35" t="n"/>
+      <c r="H23" s="27">
+        <f>IFERROR(ROUND(C23*G23*12*$B$9,0),"")</f>
+        <v/>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>一般就労移行者数と連動</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>就労選択支援</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="n"/>
+      <c r="D24" s="35" t="n"/>
+      <c r="E24" s="35" t="n"/>
+      <c r="F24" s="35" t="n"/>
+      <c r="G24" s="35" t="n"/>
+      <c r="H24" s="27">
+        <f>IFERROR(ROUND(C24*G24*12*$B$9,0),"")</f>
+        <v/>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>令和7年10月開始。圏域事業所の有無を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>児童発達支援</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>人日／月</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="n"/>
+      <c r="D25" s="35" t="n"/>
+      <c r="E25" s="35" t="n"/>
+      <c r="F25" s="35" t="n"/>
+      <c r="G25" s="35" t="n"/>
+      <c r="H25" s="27">
+        <f>IFERROR(ROUND(C25*G25*12*$B$9,0),"")</f>
+        <v/>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度は請求1件。就学に伴う移行の可能性（要確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>放課後等デイサービス</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>人日／月</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="35" t="n"/>
+      <c r="E26" s="35" t="n"/>
+      <c r="F26" s="35" t="n"/>
+      <c r="G26" s="35" t="n"/>
+      <c r="H26" s="27">
+        <f>IFERROR(ROUND(C26*G26*12*$B$9,0),"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>令和7年度は請求27件。就学に伴う流入の可能性（要確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>保育所等訪問支援</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>人／月</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="35" t="n"/>
+      <c r="E27" s="35" t="n"/>
+      <c r="F27" s="35" t="n"/>
+      <c r="G27" s="35" t="n"/>
+      <c r="H27" s="27">
+        <f>IFERROR(ROUND(C27*G27*12*$B$9,0),"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度に初めて実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
           <t>障がい児相談支援</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>人／月</t>
         </is>
       </c>
-      <c r="C22" s="28" t="n"/>
-      <c r="D22" s="29" t="n"/>
-      <c r="E22" s="29" t="n"/>
-      <c r="F22" s="29" t="n"/>
-      <c r="G22" s="29" t="n"/>
-      <c r="H22" s="27">
-        <f>IFERROR(ROUND(C22*G22*12,0),"")</f>
-        <v/>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="35" t="n"/>
+      <c r="E28" s="35" t="n"/>
+      <c r="F28" s="35" t="n"/>
+      <c r="G28" s="35" t="n"/>
+      <c r="H28" s="27">
+        <f>IFERROR(ROUND(C28*G28*12*$B$9,0),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>令和7年度 給付費330,460円</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="H23" s="22">
-        <f>SUM(H7:H22)</f>
-        <v/>
-      </c>
-      <c r="I23" s="20" t="inlineStr">
+      <c r="H29" s="22">
+        <f>SUM(H13:H28)</f>
+        <v/>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
         <is>
           <t>積上げによる令和11年度の年間給付費</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>見込量は「北塩原村_サービス見込量.xlsx」の03・04シートの『月間サービス量』を転記します。単価は直近の実績単価（令和7年度の給付費÷利用量）を基本とし、報酬改定が見込まれる場合は補正します。外部リンクにするとファイル移動時に壊れるため、転記は手作業としています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>2. 財源構成</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>見込量は「北塩原村_サービス見込量.xlsx」の03・04シートの『月間サービス量』を転記します。単価は直近の実績単価（令和7年度の給付費÷利用量）を基本とし、報酬改定による補正は上表1の適用倍率で一括して行います（単価欄には改定前の実績単価を入力してください）。外部リンクにするとファイル移動時に壊れるため、転記は手作業としています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>3. 財源構成</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>年度</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr"/>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>自立支援給付計</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>国庫負担</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>県負担</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>村負担</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>対令和7年度</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>区分・備考</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>令和7年度</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr"/>
-      <c r="C28" s="4" t="inlineStr"/>
-      <c r="D28" s="27">
+      <c r="B34" s="4" t="inlineStr"/>
+      <c r="C34" s="4" t="inlineStr"/>
+      <c r="D34" s="27">
         <f>'04_財源構成試算'!D11</f>
         <v/>
       </c>
-      <c r="E28" s="27">
-        <f>IFERROR(ROUND(D28*'01_負担区分マスタ'!$C$6,0),"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="27">
-        <f>IFERROR(ROUND(D28*'01_負担区分マスタ'!$D$6,0),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="27">
-        <f>IFERROR(D28-E28-F28,"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="30">
-        <f>IFERROR(D28/D$28-1,"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="E34" s="27">
+        <f>IFERROR(ROUND(D34*'01_負担区分マスタ'!$C$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="27">
+        <f>IFERROR(ROUND(D34*'01_負担区分マスタ'!$D$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="27">
+        <f>IFERROR(D34-E34-F34,"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="36">
+        <f>IFERROR(D34/D$34-1,"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>実績／受領データによる確定値</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>令和8年度</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr"/>
-      <c r="C29" s="8" t="inlineStr"/>
-      <c r="D29" s="28" t="n"/>
-      <c r="E29" s="27">
-        <f>IFERROR(ROUND(D29*'01_負担区分マスタ'!$C$6,0),"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="27">
-        <f>IFERROR(ROUND(D29*'01_負担区分マスタ'!$D$6,0),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="27">
-        <f>IFERROR(D29-E29-F29,"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="30">
-        <f>IFERROR(D29/D$28-1,"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr"/>
+      <c r="C35" s="8" t="inlineStr"/>
+      <c r="D35" s="28" t="n"/>
+      <c r="E35" s="27">
+        <f>IFERROR(ROUND(D35*'01_負担区分マスタ'!$C$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="27">
+        <f>IFERROR(ROUND(D35*'01_負担区分マスタ'!$D$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="27">
+        <f>IFERROR(D35-E35-F35,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="36">
+        <f>IFERROR(D35/D$34-1,"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>見込／村の最新見込を受領して入力する</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>令和9年度</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr"/>
-      <c r="C30" s="4" t="inlineStr"/>
-      <c r="D30" s="28" t="n"/>
-      <c r="E30" s="27">
-        <f>IFERROR(ROUND(D30*'01_負担区分マスタ'!$C$6,0),"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="27">
-        <f>IFERROR(ROUND(D30*'01_負担区分マスタ'!$D$6,0),"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="27">
-        <f>IFERROR(D30-E30-F30,"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="30">
-        <f>IFERROR(D30/D$28-1,"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="28" t="n"/>
+      <c r="E36" s="27">
+        <f>IFERROR(ROUND(D36*'01_負担区分マスタ'!$C$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="27">
+        <f>IFERROR(ROUND(D36*'01_負担区分マスタ'!$D$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="27">
+        <f>IFERROR(D36-E36-F36,"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="36">
+        <f>IFERROR(D36/D$34-1,"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>推計／積上げ結果を入力する（次期計画1年目）</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>令和10年度</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr"/>
-      <c r="C31" s="8" t="inlineStr"/>
-      <c r="D31" s="28" t="n"/>
-      <c r="E31" s="27">
-        <f>IFERROR(ROUND(D31*'01_負担区分マスタ'!$C$6,0),"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="27">
-        <f>IFERROR(ROUND(D31*'01_負担区分マスタ'!$D$6,0),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="27">
-        <f>IFERROR(D31-E31-F31,"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="30">
-        <f>IFERROR(D31/D$28-1,"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr"/>
+      <c r="C37" s="8" t="inlineStr"/>
+      <c r="D37" s="28" t="n"/>
+      <c r="E37" s="27">
+        <f>IFERROR(ROUND(D37*'01_負担区分マスタ'!$C$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="27">
+        <f>IFERROR(ROUND(D37*'01_負担区分マスタ'!$D$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="27">
+        <f>IFERROR(D37-E37-F37,"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="36">
+        <f>IFERROR(D37/D$34-1,"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
         <is>
           <t>推計／積上げ結果を入力する（次期計画2年目）</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>令和11年度</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr"/>
-      <c r="C32" s="4" t="inlineStr"/>
-      <c r="D32" s="27">
-        <f>H23</f>
-        <v/>
-      </c>
-      <c r="E32" s="27">
-        <f>IFERROR(ROUND(D32*'01_負担区分マスタ'!$C$6,0),"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="27">
-        <f>IFERROR(ROUND(D32*'01_負担区分マスタ'!$D$6,0),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="27">
-        <f>IFERROR(D32-E32-F32,"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="30">
-        <f>IFERROR(D32/D$28-1,"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr"/>
+      <c r="C38" s="4" t="inlineStr"/>
+      <c r="D38" s="27">
+        <f>H29</f>
+        <v/>
+      </c>
+      <c r="E38" s="27">
+        <f>IFERROR(ROUND(D38*'01_負担区分マスタ'!$C$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="27">
+        <f>IFERROR(ROUND(D38*'01_負担区分マスタ'!$D$6,0),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="27">
+        <f>IFERROR(D38-E38-F38,"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="36">
+        <f>IFERROR(D38/D$34-1,"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>推計／上表の積上げ合計を自動参照（目標年度）</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>3. 参考：伸び率による推計（第3層の補正にのみ用いる）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>4. 参考：伸び率による推計（第3層の補正にのみ用いる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>年度</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>介護給付費</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>前年度比</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>障害児給付費</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>前年度比</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>令和2年度</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B42" s="5" t="n">
         <v>36002274</v>
       </c>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="5" t="n">
+      <c r="C42" s="37" t="n"/>
+      <c r="D42" s="5" t="n">
         <v>746064</v>
       </c>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr"/>
-      <c r="H36" s="4" t="inlineStr"/>
-      <c r="I36" s="4" t="inlineStr">
+      <c r="E42" s="37" t="n"/>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>基準年度</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>令和3年度</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n">
+      <c r="B43" s="9" t="n">
         <v>45991635</v>
       </c>
-      <c r="C37" s="32" t="n">
+      <c r="C43" s="38" t="n">
         <v>0.277</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D43" s="9" t="n">
         <v>3254621</v>
       </c>
-      <c r="E37" s="32" t="n">
+      <c r="E43" s="38" t="n">
         <v>3.362</v>
       </c>
-      <c r="F37" s="8" t="inlineStr"/>
-      <c r="G37" s="8" t="inlineStr"/>
-      <c r="H37" s="8" t="inlineStr"/>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr"/>
+      <c r="G43" s="8" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr"/>
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>共同生活援助・就労継続支援B型の増</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>令和4年度</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B44" s="5" t="n">
         <v>44234021</v>
       </c>
-      <c r="C38" s="31" t="n">
+      <c r="C44" s="37" t="n">
         <v>-0.038</v>
       </c>
-      <c r="D38" s="5" t="n">
+      <c r="D44" s="5" t="n">
         <v>4030423</v>
       </c>
-      <c r="E38" s="31" t="n">
+      <c r="E44" s="37" t="n">
         <v>0.238</v>
       </c>
-      <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr"/>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>障害児給付費のピーク</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>令和5年度</t>
         </is>
       </c>
-      <c r="B39" s="9" t="n">
+      <c r="B45" s="9" t="n">
         <v>44419974</v>
       </c>
-      <c r="C39" s="32" t="n">
+      <c r="C45" s="38" t="n">
         <v>0.004</v>
       </c>
-      <c r="D39" s="9" t="n">
+      <c r="D45" s="9" t="n">
         <v>3577832</v>
       </c>
-      <c r="E39" s="32" t="n">
+      <c r="E45" s="38" t="n">
         <v>-0.112</v>
       </c>
-      <c r="F39" s="8" t="inlineStr"/>
-      <c r="G39" s="8" t="inlineStr"/>
-      <c r="H39" s="8" t="inlineStr"/>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr"/>
+      <c r="G45" s="8" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr"/>
+      <c r="I45" s="8" t="inlineStr">
         <is>
           <t>ほぼ横ばい</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>令和6年度</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B46" s="5" t="n">
         <v>52698808</v>
       </c>
-      <c r="C40" s="31" t="n">
+      <c r="C46" s="37" t="n">
         <v>0.186</v>
       </c>
-      <c r="D40" s="5" t="n">
+      <c r="D46" s="5" t="n">
         <v>1641275</v>
       </c>
-      <c r="E40" s="31" t="n">
+      <c r="E46" s="37" t="n">
         <v>-0.541</v>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr"/>
-      <c r="H40" s="4" t="inlineStr"/>
-      <c r="I40" s="4" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr">
         <is>
           <t>介護は大幅増。障害児の減は就学移行の可能性</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>令和7年度</t>
         </is>
       </c>
-      <c r="B41" s="9" t="n">
+      <c r="B47" s="9" t="n">
         <v>53877076</v>
       </c>
-      <c r="C41" s="32" t="n">
+      <c r="C47" s="38" t="n">
         <v>0.022</v>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="D47" s="9" t="n">
         <v>1635703</v>
       </c>
-      <c r="E41" s="32" t="n">
+      <c r="E47" s="38" t="n">
         <v>-0.003</v>
       </c>
-      <c r="F41" s="8" t="inlineStr"/>
-      <c r="G41" s="8" t="inlineStr"/>
-      <c r="H41" s="8" t="inlineStr"/>
-      <c r="I41" s="8" t="inlineStr">
+      <c r="F47" s="8" t="inlineStr"/>
+      <c r="G47" s="8" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr"/>
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>介護の伸びは鈍化</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="62" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="48" ht="62" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>介護給付費の前年度比は＋27.7％から−3.8％まで振れており、令和2〜7年度のCAGRは＋8.4％、直近1年は＋2.2％です。いずれも単一値として将来4年に当てはめる根拠は弱く、本表は伸び率の不安定さを示す参考資料として置いています。障害児給付費の減少は、令和6・7年度に児童発達支援が減り放課後等デイサービスが増えていることから、対象児童の就学に伴う移行である可能性があります（受給者単位の確認が必要）。ニーズの減少と断定しないでください。前回計画課題整理でも「1人の利用開始・終了で実績が大きく動くため、機械的な伸び率推計を避ける」ことを方針としています。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="11">
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A11:I11"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A32:I32"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="D7:I7"/>
+    <mergeCell ref="D8:I8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
